--- a/Mantenimiento/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/Mantenimiento/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -535,11 +530,6 @@
       </c>
       <c r="K2" t="n">
         <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -550,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,11 +577,6 @@
       </c>
       <c r="K3" t="n">
         <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -602,7 +587,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -639,11 +624,6 @@
       </c>
       <c r="K4" t="n">
         <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -654,7 +634,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -691,11 +671,6 @@
       </c>
       <c r="K5" t="n">
         <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -706,7 +681,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -743,11 +718,6 @@
       </c>
       <c r="K6" t="n">
         <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -758,7 +728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -795,11 +765,6 @@
       </c>
       <c r="K7" t="n">
         <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -810,7 +775,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -847,11 +812,6 @@
       </c>
       <c r="K8" t="n">
         <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -862,7 +822,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MADRE_DE_DIOS</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -899,11 +859,6 @@
       </c>
       <c r="K9" t="n">
         <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
+++ b/Mantenimiento/excels/MADRE_DE_DIOS-TAMBOPATA-TAMBOPATA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>52020 CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.602946</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-69.212059</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1147</v>
-      </c>
-      <c r="J2" t="n">
-        <v>53</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.602946</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-69.212059</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>296 LAS PALMERAS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.59045</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-69.19264</v>
-      </c>
-      <c r="I3" t="n">
-        <v>311</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.59045</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-69.19264</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>310 RAYITOS DEL SOL</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.593892</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-69.197019</v>
-      </c>
-      <c r="I4" t="n">
-        <v>250</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.593892</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-69.197019</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>LA PASTORA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.585947</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-69.21302</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1325</v>
-      </c>
-      <c r="J5" t="n">
-        <v>60</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.585947</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-69.21302</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>FAUSTINO MALDONADO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.59756</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-69.17791</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1656</v>
-      </c>
-      <c r="J6" t="n">
-        <v>64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.59756</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-69.17791</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>CAP. ALIPIO PONCE VASQUEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.601875</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-69.196872</v>
-      </c>
-      <c r="I7" t="n">
-        <v>473</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.601875</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-69.196872</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.58876</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-69.19971</v>
-      </c>
-      <c r="I8" t="n">
-        <v>304</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.58876</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-69.19971</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>NIÑOS DE JESUS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.59801</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-69.18612</v>
-      </c>
-      <c r="I9" t="n">
-        <v>247</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.59801</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-69.18612</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
